--- a/Internship_artifacts/Internship_artifacts/Unit_Test_Plan.xlsx
+++ b/Internship_artifacts/Internship_artifacts/Unit_Test_Plan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhik\Downloads\Internship_artifacts\Internship_artifacts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhik\Desktop\Veridict\Internship_artifacts\Internship_artifacts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB48CE5E-4E12-4E67-9FAD-8F7CCC7A22DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D17EC2C-A260-42C1-90A8-1DBCC8992B92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C3B83BB6-2AB9-4547-8541-9F6969E92BF1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="51">
   <si>
     <t>Actual Result</t>
   </si>
@@ -127,13 +127,73 @@
   </si>
   <si>
     <t>Complete evaluation with scores and reasoning is generated successfully.</t>
+  </si>
+  <si>
+    <t>Batch CSV Evaluation Test</t>
+  </si>
+  <si>
+    <t>Upload a CSV containing multiple question-answer pairs and start batch evaluation.</t>
+  </si>
+  <si>
+    <t>Valid CSV file with required columns is available.</t>
+  </si>
+  <si>
+    <t>All valid records are processed and individual evaluation results are generated.</t>
+  </si>
+  <si>
+    <t>Batch PDF Evaluation Test</t>
+  </si>
+  <si>
+    <t>Upload a supported Digital QA PDF and run batch evaluation.</t>
+  </si>
+  <si>
+    <t>Valid structured PDF containing question-answer data is available.</t>
+  </si>
+  <si>
+    <t>PDF data is parsed successfully and evaluations are generated.</t>
+  </si>
+  <si>
+    <t>Dashboard Analytics Test</t>
+  </si>
+  <si>
+    <t>Open the dashboard and verify evaluation statistics, dimension scores, verdict distribution, hallucination metrics, and trends.</t>
+  </si>
+  <si>
+    <t>Evaluation records are available for the authenticated user.</t>
+  </si>
+  <si>
+    <t>Dashboard displays correct analytics and visualizations.</t>
+  </si>
+  <si>
+    <t>Evaluation Report Export Test</t>
+  </si>
+  <si>
+    <t>Generate and open a PDF report for a completed batch evaluation.</t>
+  </si>
+  <si>
+    <t>Completed batch evaluation with valid results is available.</t>
+  </si>
+  <si>
+    <t>PDF contains project details, evaluation results, dimension scores, hallucination analysis, verdicts, and recommendations.</t>
+  </si>
+  <si>
+    <t>Authentication &amp; User Isolation Test</t>
+  </si>
+  <si>
+    <t>Log in as an authenticated user and access evaluation/history data.</t>
+  </si>
+  <si>
+    <t>Valid user account and protected API endpoints are available.</t>
+  </si>
+  <si>
+    <t>User can access their own data and cannot access another user's evaluation records.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -141,22 +201,7 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="4"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
-      <color theme="4"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -170,12 +215,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.39997558519241921"/>
+        <fgColor theme="8" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -183,38 +228,16 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -531,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF95B16C-182C-4757-B929-A728708A2DB0}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.109375" customWidth="1"/>
@@ -542,153 +565,245 @@
     <col min="6" max="6" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="76.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="53.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="64.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="62.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
+      <c r="F7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="52.8" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
